--- a/vorlagen/rissprotokoll-rissbeobachtung/rissprotokoll-rissbeobachtung.xlsx
+++ b/vorlagen/rissprotokoll-rissbeobachtung/rissprotokoll-rissbeobachtung.xlsx
@@ -951,7 +951,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grundlagen: Frössel: Risse in Gebäuden, 2. Auflage 2025, S. 117-125, 147, 371 · Schulz: Architektur der Bauschäden, 4. Auflage 2020, S. 479-480 · Stahr (Hrsg.): Bausanierung, 7. Auflage 2022, S. 258 · Hestermann/Rongen: Frick/Knöll Baukonstruktionslehre 1, 37. Auflage 2025, S. 64 · WTA-Merkblatt 2-4-14/D, Beurteilung und Instandsetzung gerissener Putze an Fassaden · DIN 4150-3:2016-12, Erschütterungen im Bauwesen - Teil 3: Einwirkungen auf bauliche Anlagen · Bayerisches Landesamt für Umwelt, Hinweise zu Rissmonitoren</t>
+          <t>Grundlagen: Frössel: Risse in Gebäuden, 2. Auflage 2025, S. 117-125, 147, 371 · Schulz: Architektur der Bauschäden, 4. Auflage 2020, S. 479-480 · Stahr (Hrsg.): Bausanierung, 7. Auflage 2022, S. 258 · Hestermann/Rongen: Frick/Knöll Baukonstruktionslehre 1, 37. Auflage 2025, S. 64 · WTA-Merkblatt 2-4-14/D mit dem Titel „Beurteilung und Instandsetzung gerissener Putze an Fassaden“ · DIN 4150-3:2016-12, Erschütterungen im Bauwesen - Teil 3: Einwirkungen auf bauliche Anlagen · Bayerisches Landesamt für Umwelt, Hinweise zu Rissmonitoren</t>
         </is>
       </c>
     </row>
